--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>29497.97</v>
+        <v>29308.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20047.08</v>
+        <v>19407.85</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>673.88</v>
+        <v>660.59</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>28088.19</v>
+        <v>28169.96</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>603876.53</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>443.19</v>
+        <v>448.64</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19084.82</v>
+        <v>19319.71</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>33732.56</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>278.43</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45105.94</v>
+        <v>45694.56</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>202.19</v>
+        <v>202.82</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6415.07</v>
+        <v>6387.51</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10694.74</v>
+        <v>10630.64</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8578.07</v>
+        <v>8461.450000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6439.12</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7798.24</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5637.02</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1782.46</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>8321.84</v>
+        <v>8302.950000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>75.42</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2932.6</v>
+        <v>2941.94</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>401052.58</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1582.94</v>
+        <v>1593.87</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>11980.56</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1915.02</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1162.3</v>
+        <v>1146.81</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>77265.00999999999</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1649.35</v>
+        <v>1624.92</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2792.79</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>404.95</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29002.01</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>97.75</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>48107.72</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>27326.34</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>429.66</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>214.83</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32224.45</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7218.28</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>144.53</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7680.67</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6586.68</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,68 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11278.56</v>
+        <v>11354.05</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1385462-131-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>11707.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metropolitana" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metropolitana" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>5522-38-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>MARCELO FABIAN</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6511.14</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5522-38-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7885.46</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="18">
@@ -2283,7 +2283,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>1549-2913-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>OSSAFERNANDEZ SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.725.099-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>409.01</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1549-2913-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>OSSAFERNANDEZ SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.725.099-1</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>29292.43</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>98.25</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>48352.86</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="35">
@@ -3076,7 +3076,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,7 +3131,1166 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
+        <v>156443.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1390255-11-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>65.165.009-7</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Cesar Ramirez e hijo limitada</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>77.991.710-k</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>48115.83</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>564953-778-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>5594.68</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1375758-63-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>61.981.300-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>11321</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1153624-116-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>62.000.670-K</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>327.07</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2792-553-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>FEBGIP SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>29566.36</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1375758-74-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.981.300-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>9308.790000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>545774-39-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.070.800-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>39379.12</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1385462-131-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
         <v>11707.46</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1057499-434-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">esteban jesus </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.252.815-0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>62389.65</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3894-78-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>69.071.400-0</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>21782.46</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1260-124-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.923.200-3</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>26138.95</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>5522-84-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>8801.280000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3474-488-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>33034.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1057499-445-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>9554.450000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4650-122-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>272.21</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1057499-443-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>20687.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>967490-77-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>60.505.000-K</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>11737.55</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1057499-444-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.608.108-K</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>9472.790000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2793-854-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>36806.65</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2791-56-CM26</t>
+          <t>3654-93-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +961,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>77.854.171-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>34181.63</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3654-93-CM26</t>
+          <t>2791-56-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>282.14</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="11">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5522-38-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7885.46</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>5522-38-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>6511.14</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="18">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>1057387-333-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.602.223-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO SALUD ARAUCANIA HOSPITAL DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>12017.6</v>
+        <v>66607.96000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1525570-26-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.229.008-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNIT</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1909.96</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5522-57-CM26</t>
+          <t>1525570-26-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>65.229.008-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MARCELO FABIAN</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1146.81</v>
+        <v>1909.96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4794-74-CM26</t>
+          <t>5522-57-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TRANSPORTES SANTIAGO S A</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.621.600-1</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>75752.64</v>
+        <v>1146.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5178-2776-CM26</t>
+          <t>4794-74-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TRANSPORTES SANTIAGO S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>78.621.600-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1624.92</v>
+        <v>75752.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>837-410-CM26</t>
+          <t>5178-2776-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,27 +2232,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.003.000-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO MEDICO LEGAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2803.69</v>
+        <v>1624.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1549-2913-CM26</t>
+          <t>837-410-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,22 +2298,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.003.000-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO MEDICO LEGAL</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OSSAFERNANDEZ SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.725.099-1</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>29292.43</v>
+        <v>2803.69</v>
       </c>
     </row>
     <row r="32">
@@ -2405,7 +2405,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>1549-2913-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,22 +2420,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>OSSAFERNANDEZ SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.725.099-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>48352.86</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>98.25</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2791-98-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>27432.71</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>2791-98-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>427.48</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5485-481-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>216.23</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>5485-481-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>32122.67</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTR</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>7203.81</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="40">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMISIÓN CHILENA DEL COBRE </t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2893,7 +2893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7638.09</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2793-734-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6554.29</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>2793-734-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11354.05</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1306643-258-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>156443.2</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1390255-11-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Cesar Ramirez e hijo limitada</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.991.710-k</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>48115.83</v>
+        <v>156443.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>1390255-11-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Cesar Ramirez e hijo limitada</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.991.710-k</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5594.68</v>
+        <v>48115.83</v>
       </c>
     </row>
     <row r="47">
@@ -3320,7 +3320,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1153624-116-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>327.07</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2792-553-CM26</t>
+          <t>1153624-116-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3396,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>29566.36</v>
+        <v>327.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1375758-74-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>77.864.159-3</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>9308.790000000001</v>
+        <v>29566.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>545774-39-CM26</t>
+          <t>1375758-74-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>39379.12</v>
+        <v>9308.790000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>545774-39-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11707.46</v>
+        <v>39379.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057499-434-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">esteban jesus </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.252.815-0</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>62389.65</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3894-78-CM26</t>
+          <t>1057499-434-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t xml:space="preserve">esteban jesus </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.252.815-0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>21782.46</v>
+        <v>62389.65</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>3894-78-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>26138.95</v>
+        <v>21782.46</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5522-84-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8801.280000000001</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>5522-84-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>33034.99</v>
+        <v>8801.280000000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4011,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>272.21</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>20687.7</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>11737.55</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,7 +4290,1105 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
+        <v>11737.55</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2793-854-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>36806.65</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1388961-663-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>65.118.035-K</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>8793.049999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1385462-164-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>13606.17</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>5485-620-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>301.09</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2793-877-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.255.400-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>15811.97</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3316-189-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.979.960-7</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>15283.35</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2490-186-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.070.300-9</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>5628.54</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>5485-650-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>LUCANO RENT A CAR S.A.</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.813.177-5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>97.03</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>5485-657-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>300.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>5522-93-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>4534.31</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1300-294-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.961.000-8</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>637.6799999999999</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1121-99-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.706.000-0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>173.73</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2735-1056-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>69.255.200-8</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>55142.84</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1485217-157-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.981.300-6</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>10021.01</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>5522-94-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>15493.7</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2735-1197-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.255.200-8</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>27536.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>188-635-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>70.933.700-9</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>12369.05</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1121-106-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.706.000-0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>165.18</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -941,7 +949,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3654-93-CM26</t>
+          <t>2791-56-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,17 +969,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +989,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +1004,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>282.14</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2791-56-CM26</t>
+          <t>3654-93-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1022,17 +1030,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,22 +1050,26 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.854.171-8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>34181.63</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="11">
@@ -1111,7 +1123,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1310,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2111,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2359,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2424,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2466,7 +2502,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2522,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2542,32 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>48352.86</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,12 +2592,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,28 +2607,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>98.25</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2791-98-CM26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,22 +2647,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2672,32 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>27432.71</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1153624-91-CM26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2712,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2722,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2737,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2752,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>427.48</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5485-481-CM26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2773,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2758,20 +2806,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>216.23</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2792-412-CM26</t>
+          <t>2791-98-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2838,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2811,12 +2863,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2878,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>32122.67</v>
+        <v>27432.71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1153624-91-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2899,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2909,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2924,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2939,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>144.24</v>
+        <v>427.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>5485-481-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2960,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2970,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,28 +2985,32 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7203.81</v>
+        <v>216.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2407-490-CM26</t>
+          <t>3894-54-SE26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +3025,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,12 +3035,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.071.200-8</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENCA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2994,28 +3050,32 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7638.09</v>
+        <v>12849.07</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2793-734-CM26</t>
+          <t>2792-412-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3090,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3055,28 +3115,32 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6554.29</v>
+        <v>32122.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1549-3384-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,22 +3155,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3180,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3195,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>11354.05</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1306643-258-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3211,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,12 +3226,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.254.200-2</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3241,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3256,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>156443.2</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1390255-11-CM26</t>
+          <t>2407-490-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,27 +3272,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>69.071.200-8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
+          <t>I MUNICIPALIDAD DE RENCA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,28 +3302,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Cesar Ramirez e hijo limitada</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.991.710-k</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>48115.83</v>
+        <v>7638.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1375758-63-CM26</t>
+          <t>2793-734-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,27 +3337,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3314,13 +3382,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>11321</v>
+        <v>6554.29</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>1549-3384-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3330,12 +3398,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3345,12 +3413,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3368,20 +3436,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>5594.68</v>
+        <v>11354.05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1153624-116-CM26</t>
+          <t>1306643-258-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,22 +3468,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>69.254.200-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,28 +3493,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>327.07</v>
+        <v>156443.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2792-553-CM26</t>
+          <t>1390255-11-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,22 +3533,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>65.165.009-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SEGURIDAD CIUDADANA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3558,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>Cesar Ramirez e hijo limitada</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
+          <t>77.991.710-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3573,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>29566.36</v>
+        <v>48115.83</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1375758-74-CM26</t>
+          <t>1375758-63-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3594,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3558,13 +3634,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9308.790000000001</v>
+        <v>11321</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>545774-39-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3655,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3589,12 +3665,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,28 +3680,32 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>39379.12</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1153624-116-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3720,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3745,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3760,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>11707.46</v>
+        <v>327.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057499-434-CM26</t>
+          <t>2792-553-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3781,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3791,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,28 +3806,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">esteban jesus </t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.252.815-0</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>62389.65</v>
+        <v>29566.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3894-78-CM26</t>
+          <t>1375758-74-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3846,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3871,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3886,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>21782.46</v>
+        <v>9308.790000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>545774-39-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3907,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3917,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3947,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>26138.95</v>
+        <v>39379.12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5522-84-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,7 +3968,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3978,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,28 +3993,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8801.280000000001</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>1057499-434-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +4033,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +4058,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t xml:space="preserve">esteban jesus </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.252.815-0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +4073,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>272.21</v>
+        <v>62389.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>3894-78-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4094,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4104,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4119,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4134,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>33034.99</v>
+        <v>21782.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4155,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,12 +4165,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4180,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4195,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>5522-84-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4216,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4226,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4241,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4256,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>8801.280000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4194,17 +4282,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4302,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4317,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>20687.7</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4255,12 +4343,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4275,12 +4363,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4378,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>11737.55</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2793-854-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4399,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4409,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4344,20 +4432,24 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>36806.65</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1388961-663-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4459,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4474,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,28 +4489,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8793.049999999999</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1385462-164-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4428,27 +4524,27 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4554,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4569,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>13606.17</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5485-620-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4489,12 +4585,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4600,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,28 +4615,32 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>301.09</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2793-877-CM26</t>
+          <t>2793-854-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4550,12 +4650,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4580,28 +4680,32 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>15811.97</v>
+        <v>36806.65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>1388961-663-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4720,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4745,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4760,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>15283.35</v>
+        <v>8793.049999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2490-186-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4781,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4791,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,28 +4806,32 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5628.54</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5485-650-CM26</t>
+          <t>5485-620-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4846,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4763,12 +4871,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LUCANO RENT A CAR S.A.</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.813.177-5</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4886,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>97.03</v>
+        <v>301.09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5485-657-CM26</t>
+          <t>2793-877-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4907,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4917,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4932,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4947,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>300.99</v>
+        <v>15811.97</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5522-93-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4968,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4993,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +5008,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>4534.31</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1300-294-CM26</t>
+          <t>2490-186-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +5029,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +5054,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +5069,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>637.6799999999999</v>
+        <v>5628.54</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1121-99-CM26</t>
+          <t>5485-650-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +5090,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +5100,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5115,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>LUCANO RENT A CAR S.A.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.813.177-5</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5130,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>173.73</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2735-1056-CM26</t>
+          <t>5485-657-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5151,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5161,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5176,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5191,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>55142.84</v>
+        <v>300.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1485217-157-CM26</t>
+          <t>5522-93-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5212,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5222,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5237,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5252,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>10021.01</v>
+        <v>4534.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5522-94-CM26</t>
+          <t>1300-294-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5273,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5298,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5313,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>15493.7</v>
+        <v>637.6799999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2735-1197-CM26</t>
+          <t>1121-99-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5334,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5344,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5359,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5374,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>27536.25</v>
+        <v>173.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>188-635-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5395,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5405,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>70.933.700-9</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,28 +5420,32 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>12369.05</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1121-106-CM26</t>
+          <t>1485217-157-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5460,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5470,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5485,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,6 +5500,250 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
+        <v>10021.01</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>5522-94-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>15493.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2735-1197-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.255.200-8</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>27536.25</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>188-635-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>70.933.700-9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE EDUC SALUD CULTURA Y RECREACION DE LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>12369.05</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1121-106-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>61.706.000-0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>arriendo</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
         <v>165.18</v>
       </c>
     </row>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -997,7 +997,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1249,7 +1253,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2502,7 +2510,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2735-849-SE26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2527,12 +2535,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2542,17 +2550,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2561,13 +2569,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38722.38</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2735-850-SE26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2587,17 +2595,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2607,32 +2615,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>82539.53</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2735-872-SE26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2691,13 +2695,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>28920.36</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2717,17 +2721,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2737,28 +2741,32 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>48352.86</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2783,12 +2791,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2798,17 +2806,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.537-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2817,7 +2825,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>98.25</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="39">
@@ -2871,7 +2879,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3140,7 +3152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3160,17 +3172,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3180,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3195,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7203.81</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3221,17 +3233,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3241,12 +3253,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3256,7 +3268,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>144.24</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="46">
@@ -4323,7 +4335,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4348,12 +4360,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4363,28 +4375,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>33034.99</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4409,12 +4425,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4424,17 +4440,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4443,7 +4459,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="65">
@@ -4514,7 +4530,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>967490-77-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4534,17 +4550,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4554,28 +4570,32 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>11737.55</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>967490-77-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4595,17 +4615,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.505.000-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4615,26 +4635,22 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.310.505-9</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>11737.55</v>
       </c>
     </row>
     <row r="68">
@@ -4953,7 +4969,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>2490-186-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4973,17 +4989,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4993,12 +5009,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5008,13 +5024,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>15283.35</v>
+        <v>5628.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2490-186-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5034,17 +5050,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5054,12 +5070,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5069,7 +5085,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5628.54</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="75">
@@ -5445,7 +5461,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1485217-157-CM26</t>
+          <t>5522-94-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5470,12 +5486,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5500,13 +5516,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>10021.01</v>
+        <v>15493.7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5522-94-CM26</t>
+          <t>1485217-157-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5531,12 +5547,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5561,7 +5577,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>15493.7</v>
+        <v>10021.01</v>
       </c>
     </row>
     <row r="83">
@@ -5745,6 +5761,71 @@
       </c>
       <c r="M85" s="2" t="n">
         <v>165.18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1300-317-SE26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.961.000-8</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>866.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>1255790-68-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>65.589.950-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>611308.61</v>
+        <v>19319.71</v>
       </c>
     </row>
     <row r="7">
@@ -888,7 +888,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1255790-68-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.589.950-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>19319.71</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="9">
@@ -1396,7 +1396,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2674-396-CM26</t>
+          <t>5522-38-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.072.900-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1436,32 +1436,28 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6511.14</v>
+        <v>7885.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5522-38-CM26</t>
+          <t>2674-396-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1486,12 +1482,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.072.900-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1501,28 +1497,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>FEBGIP SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>77.864.159-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7885.46</v>
+        <v>6511.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1375758-42-CM26</t>
+          <t>5522-39-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5658.37</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5522-39-CM26</t>
+          <t>1375758-42-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1789.21</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="20">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5485-472-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2550,17 +2550,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.366.537-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2569,13 +2569,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>98.25</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3553-292-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.402.000-8</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2615,28 +2615,32 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>48352.86</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2735-849-SE26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2695,13 +2699,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>38722.38</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2735-850-SE26</t>
+          <t>3553-292-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2721,17 +2725,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.402.000-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2741,32 +2745,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>83.547.100-4</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>82539.53</v>
+        <v>48352.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2735-872-SE26</t>
+          <t>5485-472-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>28920.36</v>
+        <v>98.25</v>
       </c>
     </row>
     <row r="39">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1375758-74-CM26</t>
+          <t>545774-39-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3863,17 +3863,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>69.070.800-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3898,13 +3898,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>9308.790000000001</v>
+        <v>39379.12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>545774-39-CM26</t>
+          <t>1375758-74-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.070.800-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN MIGUEL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>39379.12</v>
+        <v>9308.790000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3894-78-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>21782.46</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>3894-78-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26138.95</v>
+        <v>21782.46</v>
       </c>
     </row>
     <row r="61">
@@ -4274,7 +4274,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4294,17 +4294,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4314,28 +4314,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>272.21</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4385,7 +4389,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4394,13 +4398,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4420,17 +4424,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4440,32 +4444,28 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>33034.99</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>20687.7</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="66">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1388961-663-CM26</t>
+          <t>1385462-164-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.118.035-K</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4761,28 +4761,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8793.049999999999</v>
+        <v>13606.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1385462-164-CM26</t>
+          <t>1388961-663-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4802,17 +4806,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.118.035-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>ASOCIACION DE MUNICIPALIDADES PARA LA SEGURIDAD CIUDADANA EN LA ZONA ORIENTE</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4822,26 +4826,22 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>13606.17</v>
+        <v>8793.049999999999</v>
       </c>
     </row>
     <row r="71">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4969,7 +4969,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2490-186-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4989,17 +4989,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5024,13 +5024,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5628.54</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>2490-186-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>15283.35</v>
+        <v>5628.54</v>
       </c>
     </row>
     <row r="75">
@@ -5461,7 +5461,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5522-94-CM26</t>
+          <t>1485217-157-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5481,17 +5481,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5516,13 +5516,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>15493.7</v>
+        <v>10021.01</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1485217-157-CM26</t>
+          <t>5522-94-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>10021.01</v>
+        <v>15493.7</v>
       </c>
     </row>
     <row r="83">
@@ -5705,7 +5705,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1121-106-CM26</t>
+          <t>1300-317-SE26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5725,17 +5725,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5745,28 +5745,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>165.18</v>
+        <v>866.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1300-317-SE26</t>
+          <t>1121-106-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5791,12 +5795,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.961.000-8</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5806,26 +5810,644 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.501.690-7</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>866.25</v>
+        <v>165.18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2069-8569-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>590228.25</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1495206-7-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>10232.8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>603663-197-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>65.028.707-K</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Roberto</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>76.604.912-5</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>713.11</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>5522-105-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>77.951.690-3</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>2376.1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>5485-733-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>60.910.000-1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CHILE</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>71.31</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4650-148-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Marcelo Fabian</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>254.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1457776-43-SE26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>60.501.000-8</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>51670.16</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>5782-45-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>455.91</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>5782-48-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>813.4400000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1274188-749-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>70.934.900-7</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>30711.9</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -908,7 +908,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M96"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1255790-68-CM26</t>
+          <t>5441-182-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.589.950-2</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>19319.71</v>
+        <v>448.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5441-182-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,12 +867,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>448.64</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>1255790-68-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>65.589.950-2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACION DE PENALOLEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>611308.61</v>
+        <v>19319.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2791-56-CM26</t>
+          <t>3654-93-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -969,17 +969,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.255.400-0</t>
+          <t>61.101.034-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Municipalidad de Huechuraba</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,17 +989,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TRAVEL RENT A CAR LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>77.854.171-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>34181.63</v>
+        <v>282.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3654-93-CM26</t>
+          <t>2791-56-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.101.034-6</t>
+          <t>69.255.400-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TRAVEL RENT A CAR LIMITADA</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.854.171-8</t>
+          <t>78.973.230-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>282.14</v>
+        <v>34181.63</v>
       </c>
     </row>
     <row r="11">
@@ -1522,7 +1522,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5522-39-CM26</t>
+          <t>1375758-42-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1577,13 +1577,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1789.21</v>
+        <v>5658.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1375758-42-CM26</t>
+          <t>5522-39-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5658.37</v>
+        <v>1789.21</v>
       </c>
     </row>
     <row r="20">
@@ -2384,7 +2384,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5485-464-CM26</t>
+          <t>1549-2913-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2404,17 +2404,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2424,32 +2424,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>OSSAFERNANDEZ SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.725.099-1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>409.01</v>
+        <v>29292.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1549-2913-CM26</t>
+          <t>5485-464-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2469,17 +2465,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2489,22 +2485,26 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>OSSAFERNANDEZ SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.725.099-1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>29292.43</v>
+        <v>409.01</v>
       </c>
     </row>
     <row r="34">
@@ -3152,7 +3152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1121-73-CM26</t>
+          <t>1485217-105-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3207,13 +3207,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>144.24</v>
+        <v>7203.81</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1485217-105-CM26</t>
+          <t>1121-73-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7203.81</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="46">
@@ -3591,7 +3591,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1375758-63-CM26</t>
+          <t>564953-778-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3611,17 +3611,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.300-6</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3631,28 +3631,32 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11321</v>
+        <v>5594.68</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>564953-778-CM26</t>
+          <t>1375758-63-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3672,17 +3676,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>61.981.300-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTIAGO CENTRO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3692,26 +3696,22 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>5594.68</v>
+        <v>11321</v>
       </c>
     </row>
     <row r="53">
@@ -4091,7 +4091,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>3894-78-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4111,17 +4111,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.071.400-0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE LAMPA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4131,12 +4131,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>26138.95</v>
+        <v>21782.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3894-78-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4172,17 +4172,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.071.400-0</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAMPA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21782.46</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="61">
@@ -4274,7 +4274,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4333,13 +4333,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057499-443-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4359,17 +4359,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4379,32 +4379,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.621.909-8</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>20687.7</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4429,12 +4425,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4444,28 +4440,32 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>272.21</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4485,17 +4485,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>33034.99</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>1057499-443-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4589,7 +4589,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>20687.7</v>
       </c>
     </row>
     <row r="67">
@@ -4969,7 +4969,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3316-189-CM26</t>
+          <t>2490-186-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4994,12 +4994,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -5024,13 +5024,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>15283.35</v>
+        <v>5628.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2490-186-CM26</t>
+          <t>3316-189-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5628.54</v>
+        <v>15283.35</v>
       </c>
     </row>
     <row r="75">
@@ -5152,7 +5152,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5485-657-CM26</t>
+          <t>5522-93-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>300.99</v>
+        <v>4534.31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5522-93-CM26</t>
+          <t>5485-657-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4534.31</v>
+        <v>300.99</v>
       </c>
     </row>
     <row r="78">
@@ -6331,7 +6331,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5782-48-CM26</t>
+          <t>1300-361-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>61.961.000-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6386,13 +6386,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>813.4400000000001</v>
+        <v>1527.71</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1274188-749-CM26</t>
+          <t>5782-48-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6447,6 +6447,67 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
+        <v>813.4400000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1274188-749-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>70.934.900-7</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>76.902.907-9</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
         <v>30711.9</v>
       </c>
     </row>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/metropolitana.xlsx
@@ -5790,7 +5790,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
